--- a/reference/origins/product info/WA_Topicals_Product_Catalog_Final.xlsx
+++ b/reference/origins/product info/WA_Topicals_Product_Catalog_Final.xlsx
@@ -587,7 +587,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dragon Balm (Ceres)</t>
+          <t>Ceres</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
